--- a/data/trans_dic/IP16A08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,36</t>
+          <t>0,0; 32,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,28</t>
+          <t>0,0; 20,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 40,74</t>
+          <t>3,72; 35,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,39</t>
+          <t>0,0; 16,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,73</t>
+          <t>0,0; 37,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 33,89</t>
+          <t>3,66; 35,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 29,74</t>
+          <t>3,08; 34,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,28</t>
+          <t>0,0; 19,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 24,23</t>
+          <t>3,01; 22,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 23,41</t>
+          <t>4,39; 24,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 26,28</t>
+          <t>4,73; 25,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,89</t>
+          <t>1,19; 13,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 41,01</t>
+          <t>7,67; 40,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 36,23</t>
+          <t>8,82; 37,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 34,24</t>
+          <t>8,34; 33,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 19,25</t>
+          <t>1,68; 18,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 32,01</t>
+          <t>4,33; 31,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 24,69</t>
+          <t>2,68; 22,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 36,18</t>
+          <t>6,84; 37,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 21,43</t>
+          <t>3,8; 20,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 30,36</t>
+          <t>10,15; 31,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 25,62</t>
+          <t>8,09; 24,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 30,62</t>
+          <t>10,49; 29,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 15,47</t>
+          <t>3,52; 15,84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,76</t>
+          <t>0,0; 38,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,47</t>
+          <t>0,0; 22,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,05</t>
+          <t>0,0; 37,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 41,65</t>
+          <t>5,78; 41,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,68</t>
+          <t>0,0; 25,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,02</t>
+          <t>0,0; 50,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 26,97</t>
+          <t>3,17; 26,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 29,94</t>
+          <t>5,79; 30,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,75</t>
+          <t>1,76; 15,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 31,31</t>
+          <t>3,81; 31,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,5</t>
+          <t>1,83; 15,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 37,05</t>
+          <t>4,8; 38,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,17</t>
+          <t>0,0; 27,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 28,54</t>
+          <t>2,47; 28,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,26</t>
+          <t>0,0; 37,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 45,73</t>
+          <t>8,7; 44,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 26,49</t>
+          <t>2,81; 31,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,86</t>
+          <t>0,0; 16,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 33,6</t>
+          <t>9,27; 33,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 20,48</t>
+          <t>3,33; 21,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 17,36</t>
+          <t>3,59; 20,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,49</t>
+          <t>0,0; 20,14</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 67,86</t>
+          <t>10,64; 66,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,19</t>
+          <t>0,0; 36,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,24</t>
+          <t>0,0; 53,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,64</t>
+          <t>0,0; 58,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,7</t>
+          <t>0,0; 57,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,41; 50,6</t>
+          <t>13,23; 50,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,21</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,56</t>
+          <t>0,0; 40,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,13</t>
+          <t>0,0; 38,69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,27; 52,16</t>
+          <t>11,24; 54,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 41,48</t>
+          <t>4,16; 40,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 52,76</t>
+          <t>6,98; 54,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,28</t>
+          <t>0,0; 36,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,25; 65,51</t>
+          <t>22,75; 65,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 36,69</t>
+          <t>6,6; 36,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,05; 63,75</t>
+          <t>0,0; 62,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,41</t>
+          <t>0,0; 21,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,36; 52,68</t>
+          <t>20,56; 49,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 32,27</t>
+          <t>8,71; 32,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,81; 46,45</t>
+          <t>9,0; 46,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 18,55</t>
+          <t>1,66; 17,62</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,91</t>
+          <t>0,0; 20,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 29,09</t>
+          <t>5,31; 30,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 40,51</t>
+          <t>5,41; 39,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,5; 37,97</t>
+          <t>10,75; 37,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 23,98</t>
+          <t>2,71; 23,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 25,98</t>
+          <t>2,77; 26,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,75</t>
+          <t>0,0; 27,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 19,71</t>
+          <t>2,13; 22,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 17,33</t>
+          <t>3,03; 17,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 22,15</t>
+          <t>6,42; 22,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 27,61</t>
+          <t>4,96; 27,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,47; 23,83</t>
+          <t>8,06; 22,74</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 25,39</t>
+          <t>2,58; 23,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 26,13</t>
+          <t>3,0; 27,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,74</t>
+          <t>0,0; 21,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,34</t>
+          <t>0,0; 31,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 21,15</t>
+          <t>5,14; 22,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 40,44</t>
+          <t>11,04; 42,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,68; 36,85</t>
+          <t>11,12; 36,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 53,74</t>
+          <t>9,05; 56,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 18,46</t>
+          <t>5,94; 18,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 30,16</t>
+          <t>10,07; 29,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,87; 26,17</t>
+          <t>7,92; 26,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 37,75</t>
+          <t>7,55; 40,71</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,94; 22,33</t>
+          <t>10,7; 21,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,09; 17,45</t>
+          <t>8,13; 17,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,42; 19,74</t>
+          <t>9,4; 19,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,78</t>
+          <t>4,38; 13,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,61; 21,39</t>
+          <t>11,84; 21,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,5</t>
+          <t>8,43; 17,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,01</t>
+          <t>9,65; 20,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,2</t>
+          <t>6,51; 15,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,64; 19,96</t>
+          <t>12,68; 19,87</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,14</t>
+          <t>9,35; 15,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,7</t>
+          <t>10,78; 18,23</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,44</t>
+          <t>6,3; 12,63</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2509</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2154</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3670</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3792</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3275</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>598; 5767</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4917</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4596</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>659; 6342</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>592; 6576</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4309</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>717; 5453</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1477; 8270</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1668; 9077</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>630; 6850</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4602</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5095</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5171</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6579</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7272</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8946</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10042</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1283; 6800</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2070; 8689</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2274; 9053</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1062; 11722</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>860; 6166</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>668; 5629</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1415; 7678</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1830; 9883</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3714; 11600</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3920; 11915</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5029; 14332</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3911; 17619</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2170</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2333</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2170</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4438</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3481</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>611; 4422</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5763</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4216</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>642; 5324</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1284; 6688</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>667; 5988</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>681; 5626</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>701; 5844</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2470</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1533</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3721</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4365</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>784; 6267</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5304</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>589; 6861</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4683</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1429; 7390</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>428; 4734</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4268</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3037; 11052</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1152; 7308</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1775; 10076</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4752</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>971; 6092</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5227</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4154</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3023</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6160</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2242; 8569</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6077</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4698</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 7323</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3552</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4447</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7999</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5081</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1391; 6740</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>457; 4401</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>635; 4993</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2839</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2441; 6980</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1195; 6519</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5436</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2917</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>4752; 11505</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2534; 9445</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1601; 8301</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>352; 3751</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3754</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2793</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4190</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>6646</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>10345</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4371</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1409; 8040</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>770; 5601</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3203; 11262</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>720; 6283</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>702; 6733</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2913</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>947; 9935</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1454; 8383</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3333; 11751</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1234; 6858</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5974; 16859</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2562</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>5170</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5548</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>7732</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3842</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>669; 6099</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>637; 5869</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4565</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2557</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2049; 9097</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2396; 9216</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2781; 9109</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1059; 6628</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3908; 12137</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>4322; 12805</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3636; 12116</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1496; 8068</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>17758</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>17623</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>18609</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>42776</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13412; 26859</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>11969; 25357</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>11976; 25387</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>7776; 23123</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>17037; 31549</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>13322; 27433</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>11902; 25702</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>11853; 27454</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>34147; 53489</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>28536; 47421</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>27028; 45709</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>22666; 45449</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,5</t>
+          <t>0,0; 29,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,98</t>
+          <t>0,0; 24,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 35,84</t>
+          <t>3,61; 39,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,18</t>
+          <t>0,0; 15,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,87</t>
+          <t>0,0; 37,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 35,18</t>
+          <t>0,0; 33,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 34,24</t>
+          <t>2,97; 30,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,3</t>
+          <t>0,0; 19,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 22,91</t>
+          <t>2,95; 23,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 24,59</t>
+          <t>4,15; 23,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 25,71</t>
+          <t>4,29; 25,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 13,0</t>
+          <t>1,4; 13,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 40,64</t>
+          <t>7,7; 41,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 37,0</t>
+          <t>8,26; 36,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 33,21</t>
+          <t>8,54; 34,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 18,59</t>
+          <t>1,37; 19,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 31,05</t>
+          <t>3,39; 30,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,54</t>
+          <t>2,74; 24,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 37,12</t>
+          <t>6,53; 36,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 20,52</t>
+          <t>4,17; 20,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 31,71</t>
+          <t>9,04; 28,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 24,59</t>
+          <t>7,51; 25,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 29,89</t>
+          <t>10,57; 30,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,84</t>
+          <t>3,57; 15,48</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,17</t>
+          <t>0,0; 37,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,41</t>
+          <t>0,0; 21,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,5</t>
+          <t>0,0; 36,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 41,87</t>
+          <t>5,71; 41,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,83</t>
+          <t>0,0; 25,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,56</t>
+          <t>0,0; 50,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 26,24</t>
+          <t>3,28; 26,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 30,14</t>
+          <t>5,77; 31,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,82</t>
+          <t>1,78; 15,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 31,5</t>
+          <t>3,83; 31,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 15,29</t>
+          <t>1,85; 15,58</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 38,33</t>
+          <t>4,83; 38,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,46</t>
+          <t>0,0; 24,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 28,83</t>
+          <t>3,42; 28,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,4</t>
+          <t>0,0; 34,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 44,99</t>
+          <t>8,77; 45,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 31,06</t>
+          <t>3,04; 34,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,68</t>
+          <t>0,0; 16,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 33,72</t>
+          <t>8,76; 32,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 21,15</t>
+          <t>3,56; 22,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 20,41</t>
+          <t>3,35; 17,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,14</t>
+          <t>0,0; 17,58</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,64; 66,75</t>
+          <t>10,41; 62,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,03</t>
+          <t>0,0; 36,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,12</t>
+          <t>0,0; 54,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,5</t>
+          <t>0,0; 62,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,63</t>
+          <t>0,0; 55,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 50,56</t>
+          <t>11,42; 50,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>0,0; 21,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>0,0; 35,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,69</t>
+          <t>0,0; 36,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 54,45</t>
+          <t>11,52; 52,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 40,05</t>
+          <t>4,11; 42,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 54,84</t>
+          <t>7,01; 52,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,97</t>
+          <t>0,0; 37,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,75; 65,06</t>
+          <t>19,42; 66,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,6; 36,03</t>
+          <t>6,73; 36,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,59</t>
+          <t>8,86; 61,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,44</t>
+          <t>0,0; 24,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,56; 49,79</t>
+          <t>19,81; 51,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,71; 32,48</t>
+          <t>8,32; 30,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 46,66</t>
+          <t>11,5; 49,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 17,62</t>
+          <t>1,68; 18,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,33</t>
+          <t>0,0; 26,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 30,27</t>
+          <t>5,34; 28,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 39,31</t>
+          <t>5,13; 38,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 37,81</t>
+          <t>9,71; 35,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 23,69</t>
+          <t>2,7; 23,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 26,56</t>
+          <t>2,73; 25,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,47</t>
+          <t>0,0; 26,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 22,4</t>
+          <t>2,94; 21,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 17,45</t>
+          <t>3,04; 17,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 22,64</t>
+          <t>5,7; 22,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 27,59</t>
+          <t>5,11; 27,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,06; 22,74</t>
+          <t>7,57; 22,46</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 23,53</t>
+          <t>2,58; 23,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 27,65</t>
+          <t>2,95; 25,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,82</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,52</t>
+          <t>0,0; 35,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 22,82</t>
+          <t>5,13; 22,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,04; 42,49</t>
+          <t>11,79; 41,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,12; 36,42</t>
+          <t>10,95; 36,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 56,62</t>
+          <t>9,05; 54,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 18,45</t>
+          <t>6,19; 19,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,07; 29,84</t>
+          <t>8,94; 28,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,92; 26,38</t>
+          <t>7,64; 25,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 40,71</t>
+          <t>7,23; 37,83</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,7; 21,43</t>
+          <t>10,34; 21,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,22</t>
+          <t>8,3; 17,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 19,92</t>
+          <t>9,27; 19,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,01</t>
+          <t>4,38; 12,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,84; 21,92</t>
+          <t>11,59; 21,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,37</t>
+          <t>8,94; 18,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,65; 20,85</t>
+          <t>9,82; 20,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,07</t>
+          <t>6,53; 15,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,68; 19,87</t>
+          <t>12,26; 19,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,54</t>
+          <t>9,49; 15,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,78; 18,23</t>
+          <t>10,9; 18,17</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,63</t>
+          <t>6,62; 12,52</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3792</t>
+          <t>0; 3386</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3275</t>
+          <t>0; 3824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>598; 5767</t>
+          <t>581; 6322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4917</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4596</t>
+          <t>0; 4561</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>659; 6342</t>
+          <t>0; 6110</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>592; 6576</t>
+          <t>570; 5900</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 4264</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>717; 5453</t>
+          <t>701; 5642</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1477; 8270</t>
+          <t>1395; 7760</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1668; 9077</t>
+          <t>1516; 8890</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>630; 6850</t>
+          <t>736; 6860</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1283; 6800</t>
+          <t>1288; 6884</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2070; 8689</t>
+          <t>1940; 8620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2274; 9053</t>
+          <t>2327; 9332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1062; 11722</t>
+          <t>865; 12104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>860; 6166</t>
+          <t>672; 6146</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>668; 5629</t>
+          <t>685; 6105</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1415; 7678</t>
+          <t>1351; 7627</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1830; 9883</t>
+          <t>2010; 9640</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3714; 11600</t>
+          <t>3307; 10451</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3920; 11915</t>
+          <t>3641; 12135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5029; 14332</t>
+          <t>5069; 14680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3911; 17619</t>
+          <t>3970; 17218</t>
         </is>
       </c>
     </row>
@@ -2625,17 +2625,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3481</t>
+          <t>0; 3414</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3571</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2645,42 +2645,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>611; 4422</t>
+          <t>603; 4380</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5763</t>
+          <t>0; 5729</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>0; 4202</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>642; 5324</t>
+          <t>665; 5404</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1284; 6688</t>
+          <t>1281; 7034</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>667; 5988</t>
+          <t>674; 5944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>681; 5626</t>
+          <t>684; 5644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>701; 5844</t>
+          <t>707; 5957</t>
         </is>
       </c>
     </row>
@@ -2833,37 +2833,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>784; 6267</t>
+          <t>790; 6299</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5304</t>
+          <t>0; 4763</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>589; 6861</t>
+          <t>813; 6828</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4683</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1429; 7390</t>
+          <t>1441; 7471</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>428; 4734</t>
+          <t>464; 5213</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4268</t>
+          <t>0; 4201</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3037; 11052</t>
+          <t>2871; 10654</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1152; 7308</t>
+          <t>1229; 7604</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1775; 10076</t>
+          <t>1657; 8599</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4752</t>
+          <t>0; 4147</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>971; 6092</t>
+          <t>950; 5727</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 5291</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4154</t>
+          <t>0; 4232</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3023</t>
+          <t>0; 3236</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 6160</t>
+          <t>0; 5972</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2242; 8569</t>
+          <t>1935; 8578</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6077</t>
+          <t>0; 5755</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4698</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 7323</t>
+          <t>0; 6832</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1391; 6740</t>
+          <t>1426; 6465</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>457; 4401</t>
+          <t>452; 4661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>635; 4993</t>
+          <t>639; 4813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2839</t>
+          <t>0; 2850</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2441; 6980</t>
+          <t>2084; 7082</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1195; 6519</t>
+          <t>1218; 6678</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5436</t>
+          <t>769; 5363</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2917</t>
+          <t>0; 3348</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4752; 11505</t>
+          <t>4577; 11941</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2534; 9445</t>
+          <t>2420; 8889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1601; 8301</t>
+          <t>2046; 8749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>352; 3751</t>
+          <t>357; 4025</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4371</t>
+          <t>0; 5674</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1409; 8040</t>
+          <t>1418; 7614</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>770; 5601</t>
+          <t>731; 5447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3203; 11262</t>
+          <t>2894; 10467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>720; 6283</t>
+          <t>716; 6228</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>702; 6733</t>
+          <t>692; 6550</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2913</t>
+          <t>0; 2763</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>947; 9935</t>
+          <t>1305; 9702</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1454; 8383</t>
+          <t>1459; 8627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3333; 11751</t>
+          <t>2960; 11459</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1234; 6858</t>
+          <t>1269; 6747</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5974; 16859</t>
+          <t>5614; 16648</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>669; 6099</t>
+          <t>669; 6177</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>637; 5869</t>
+          <t>625; 5502</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4565</t>
+          <t>0; 4487</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2557</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2049; 9097</t>
+          <t>2047; 8916</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2396; 9216</t>
+          <t>2558; 9035</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2781; 9109</t>
+          <t>2740; 9077</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1059; 6628</t>
+          <t>1059; 6383</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3908; 12137</t>
+          <t>4074; 12753</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4322; 12805</t>
+          <t>3837; 12408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3636; 12116</t>
+          <t>3507; 11630</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1496; 8068</t>
+          <t>1434; 7497</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13412; 26859</t>
+          <t>12958; 26910</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11969; 25357</t>
+          <t>12225; 25543</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11976; 25387</t>
+          <t>11815; 24797</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7776; 23123</t>
+          <t>7779; 22522</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17037; 31549</t>
+          <t>16676; 31017</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13322; 27433</t>
+          <t>14124; 28594</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11902; 25702</t>
+          <t>12105; 25464</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11853; 27454</t>
+          <t>11891; 27497</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34147; 53489</t>
+          <t>32995; 52511</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28536; 47421</t>
+          <t>28961; 47480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27028; 45709</t>
+          <t>27336; 45555</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>22666; 45449</t>
+          <t>23828; 45074</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A08-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15,19%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,02</t>
+          <t>0,0; 36,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,49</t>
+          <t>3,61; 33,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 39,29</t>
+          <t>3,1; 29,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,16</t>
+          <t>0,0; 20,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,59</t>
+          <t>0,0; 24,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,9</t>
+          <t>0,0; 24,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 30,72</t>
+          <t>3,8; 40,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 19,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 23,7</t>
+          <t>3,0; 24,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 23,07</t>
+          <t>3,77; 23,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 25,18</t>
+          <t>5,13; 26,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,02</t>
+          <t>1,57; 14,75</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,6%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>18,69%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 41,15</t>
+          <t>3,35; 32,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 36,71</t>
+          <t>2,73; 24,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 34,23</t>
+          <t>6,73; 36,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 19,2</t>
+          <t>4,33; 21,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 30,95</t>
+          <t>10,84; 41,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 24,44</t>
+          <t>7,15; 36,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 36,88</t>
+          <t>7,44; 34,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 20,01</t>
+          <t>6,24; 26,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 28,57</t>
+          <t>10,11; 30,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 25,04</t>
+          <t>7,82; 25,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 30,62</t>
+          <t>10,97; 30,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 15,48</t>
+          <t>6,36; 19,33</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12,74%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,29%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15,11%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,29</t>
+          <t>5,75; 41,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,98</t>
+          <t>0,0; 23,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,89</t>
+          <t>0,0; 50,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>3,57; 28,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 38,76</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 21,47</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 37,05</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,71; 41,47</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 25,68</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3,28; 26,64</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 31,7</t>
+          <t>5,92; 29,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,71</t>
+          <t>1,77; 16,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 31,6</t>
+          <t>3,81; 31,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 15,58</t>
+          <t>1,83; 15,77</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 38,52</t>
+          <t>8,94; 45,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,66</t>
+          <t>2,65; 26,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 28,69</t>
+          <t>0,0; 18,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 45,48</t>
+          <t>4,84; 37,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 34,2</t>
+          <t>0,0; 24,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,42</t>
+          <t>4,23; 28,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 32,5</t>
+          <t>9,93; 33,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 22,0</t>
+          <t>3,41; 20,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 17,41</t>
+          <t>3,39; 17,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 22,07</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,35%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28,87%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,41; 62,76</t>
+          <t>0,0; 61,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 57,64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 37,39</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,63; 67,86</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 36,19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 54,12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 62,61</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 55,87</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,42; 50,62</t>
+          <t>12,41; 50,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,48</t>
+          <t>0,0; 22,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,02</t>
+          <t>0,0; 31,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,1</t>
+          <t>0,0; 21,81</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41,45%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>28,7%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22,92%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 52,22</t>
+          <t>18,25; 65,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 42,42</t>
+          <t>7,06; 36,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 52,86</t>
+          <t>9,05; 63,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,12</t>
+          <t>0,0; 30,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,42; 66,01</t>
+          <t>11,27; 52,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,73; 36,91</t>
+          <t>4,07; 41,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,86; 61,75</t>
+          <t>6,84; 52,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,6</t>
+          <t>0,0; 36,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,81; 51,68</t>
+          <t>20,36; 52,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 30,57</t>
+          <t>8,64; 32,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,5; 49,18</t>
+          <t>11,81; 46,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 18,91</t>
+          <t>1,37; 23,06</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,72%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>14,14%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>19,6%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,39</t>
+          <t>2,71; 23,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 28,67</t>
+          <t>2,71; 25,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 38,22</t>
+          <t>0,0; 28,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 35,14</t>
+          <t>2,25; 22,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 23,48</t>
+          <t>0,0; 19,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 25,84</t>
+          <t>5,35; 29,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,06</t>
+          <t>5,2; 40,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 21,87</t>
+          <t>10,97; 39,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,96</t>
+          <t>3,02; 17,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 22,08</t>
+          <t>6,53; 22,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 27,15</t>
+          <t>5,4; 27,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,57; 22,46</t>
+          <t>8,17; 25,28</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22,18%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28,74%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>10,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>12,07%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,18%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 23,83</t>
+          <t>4,78; 21,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 25,92</t>
+          <t>9,46; 40,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,45</t>
+          <t>10,68; 36,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,52</t>
+          <t>9,14; 56,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,13; 22,36</t>
+          <t>2,6; 25,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,79; 41,65</t>
+          <t>2,94; 26,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,95; 36,29</t>
+          <t>0,0; 21,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 54,53</t>
+          <t>0,0; 34,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,38</t>
+          <t>5,87; 18,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 28,91</t>
+          <t>10,13; 30,16</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,64; 25,32</t>
+          <t>7,87; 26,17</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 37,83</t>
+          <t>7,84; 40,5</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,48</t>
+          <t>11,61; 21,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,35</t>
+          <t>8,66; 17,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,27; 19,45</t>
+          <t>10,39; 21,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,67</t>
+          <t>6,71; 15,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,59; 21,55</t>
+          <t>10,94; 22,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,1</t>
+          <t>8,09; 17,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,66</t>
+          <t>9,42; 19,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,53; 15,09</t>
+          <t>6,81; 16,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,26; 19,5</t>
+          <t>12,64; 19,96</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,56</t>
+          <t>9,27; 16,14</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,9; 18,17</t>
+          <t>11,03; 19,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,52</t>
+          <t>7,77; 13,8</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,32 +2073,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2509</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2154</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>730</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1162</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2445</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2154</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2440</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3386</t>
+          <t>0; 4457</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>650; 6108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>581; 6322</t>
+          <t>595; 5713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4606</t>
+          <t>0; 3933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4561</t>
+          <t>0; 2843</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6110</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>570; 5900</t>
+          <t>611; 6555</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4264</t>
+          <t>0; 4099</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>701; 5642</t>
+          <t>713; 5767</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1395; 7760</t>
+          <t>1268; 7875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1516; 8890</t>
+          <t>1811; 9277</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>736; 6860</t>
+          <t>628; 5909</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3774</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4602</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5095</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5171</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3851</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9787</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1288; 6884</t>
+          <t>664; 6357</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1940; 8620</t>
+          <t>681; 6166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2327; 9332</t>
+          <t>1393; 7482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>865; 12104</t>
+          <t>1847; 9263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>672; 6146</t>
+          <t>1814; 6861</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>685; 6105</t>
+          <t>1680; 8508</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1351; 7627</t>
+          <t>2027; 9335</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2010; 9640</t>
+          <t>2419; 10096</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3307; 10451</t>
+          <t>3698; 11108</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3641; 12135</t>
+          <t>3791; 12415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5069; 14680</t>
+          <t>5259; 14682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3970; 17218</t>
+          <t>5178; 15742</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,44 +2557,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1482</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1654</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3352</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>1985</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>607; 4398</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3414</t>
+          <t>0; 5282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>631; 4949</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4507</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3334</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3528</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>603; 4380</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5729</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4202</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>665; 5404</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1281; 7034</t>
+          <t>1314; 6644</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>674; 5944</t>
+          <t>669; 6338</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>684; 5644</t>
+          <t>680; 5592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>707; 5957</t>
+          <t>639; 5502</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3721</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2470</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1533</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2994</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1745</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>790; 6299</t>
+          <t>1469; 7511</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4763</t>
+          <t>403; 4037</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>813; 6828</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4326</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1441; 7471</t>
+          <t>792; 6058</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>464; 5213</t>
+          <t>0; 4668</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>1006; 6793</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2871; 10654</t>
+          <t>3255; 11013</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1229; 7604</t>
+          <t>1180; 7078</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1657; 8599</t>
+          <t>1676; 8571</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 4996</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>793</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2196</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4893</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1791</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>1246</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>950; 5727</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5291</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0; 2979</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3642</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>970; 6192</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5250</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4232</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3236</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0; 5972</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1935; 8578</t>
+          <t>2103; 8575</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5755</t>
+          <t>0; 5950</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>0; 3685</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 6832</t>
+          <t>0; 3964</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4447</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3552</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1675</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2087</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4447</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2487</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>585</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1418</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1426; 6465</t>
+          <t>1958; 7028</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>452; 4661</t>
+          <t>1277; 6639</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>639; 4813</t>
+          <t>786; 5537</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2850</t>
+          <t>0; 3445</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2084; 7082</t>
+          <t>1396; 6456</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1218; 6678</t>
+          <t>447; 4558</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>769; 5363</t>
+          <t>623; 4804</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3348</t>
+          <t>0; 2794</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4577; 11941</t>
+          <t>4704; 12173</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2420; 8889</t>
+          <t>2512; 9384</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2046; 8749</t>
+          <t>2100; 8263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>357; 4025</t>
+          <t>261; 4405</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>1444</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3754</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2793</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10784</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5674</t>
+          <t>719; 6361</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1418; 7614</t>
+          <t>688; 6585</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>731; 5447</t>
+          <t>0; 3049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2894; 10467</t>
+          <t>947; 9312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>716; 6228</t>
+          <t>0; 4280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>692; 6550</t>
+          <t>1420; 7727</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2763</t>
+          <t>740; 5773</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1305; 9702</t>
+          <t>3321; 12012</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1459; 8627</t>
+          <t>1449; 8322</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2960; 11459</t>
+          <t>3390; 11496</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1269; 6747</t>
+          <t>1343; 6861</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5614; 16648</t>
+          <t>5906; 18275</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5170</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5548</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>2702</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2562</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1516</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>4618</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5170</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5548</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>525</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3890</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>669; 6177</t>
+          <t>1906; 8430</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>625; 5502</t>
+          <t>2052; 8772</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4487</t>
+          <t>2672; 9217</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2882</t>
+          <t>1069; 6610</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2047; 8916</t>
+          <t>673; 6583</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2558; 9035</t>
+          <t>625; 5546</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2740; 9077</t>
+          <t>0; 4548</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1059; 6383</t>
+          <t>0; 2597</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4074; 12753</t>
+          <t>3864; 12148</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3837; 12408</t>
+          <t>4347; 12941</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3507; 11630</t>
+          <t>3615; 12019</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1434; 7497</t>
+          <t>1517; 7834</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12958; 26910</t>
+          <t>16713; 30782</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12225; 25543</t>
+          <t>13676; 27640</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11815; 24797</t>
+          <t>12814; 25905</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7779; 22522</t>
+          <t>11064; 25466</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16676; 31017</t>
+          <t>13711; 27978</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14124; 28594</t>
+          <t>11906; 25693</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12105; 25464</t>
+          <t>12002; 25156</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11891; 27497</t>
+          <t>9733; 23447</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>32995; 52511</t>
+          <t>34029; 53746</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28961; 47480</t>
+          <t>28283; 49257</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27336; 45555</t>
+          <t>27656; 49384</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>23828; 45074</t>
+          <t>23936; 42490</t>
         </is>
       </c>
     </row>
